--- a/src/assets/files/personnel_model.xlsx
+++ b/src/assets/files/personnel_model.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t xml:space="preserve">Travailleurs Hautement Qualifiés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
   </si>
 </sst>
 </file>
@@ -224,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -251,6 +254,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -295,7 +303,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -308,8 +316,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -329,7 +345,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AQ66"/>
+  <dimension ref="A1:AX1005"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.09"/>
@@ -435,7 +451,7 @@
       <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
@@ -462,13 +478,13 @@
       <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="2" t="s">
@@ -480,10 +496,10 @@
       <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -506,10 +522,10 @@
       <c r="F2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="L2" s="1" t="n">
@@ -524,13 +540,13 @@
       <c r="P2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" s="4" t="s">
         <v>54</v>
       </c>
       <c r="AB2" s="1" t="n">
@@ -586,10 +602,10 @@
       <c r="F3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="L3" s="1" t="n">
@@ -604,14 +620,14 @@
       <c r="P3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="3" t="s">
-        <v>54</v>
+      <c r="AA3" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>0</v>
@@ -649,594 +665,4373 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="M4" s="1"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AW4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="AX4" s="0" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
       <c r="M5" s="1"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AW5" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX5" s="0" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
       <c r="M6" s="1"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4"/>
       <c r="M7" s="1"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
       <c r="M8" s="1"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4"/>
       <c r="M9" s="1"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4"/>
       <c r="M10" s="1"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
       <c r="M11" s="1"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="3"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4"/>
       <c r="M12" s="1"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="3"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
       <c r="M13" s="1"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="3"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
       <c r="M14" s="1"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="3"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
       <c r="M15" s="1"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="3"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="4"/>
       <c r="M16" s="1"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="3"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="4"/>
       <c r="M17" s="1"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="3"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4"/>
       <c r="M18" s="1"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="3"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4"/>
       <c r="M19" s="1"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="3"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="4"/>
       <c r="M20" s="1"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="3"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="4"/>
       <c r="M21" s="1"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="4"/>
       <c r="M22" s="1"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="3"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4"/>
       <c r="M23" s="1"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="3"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="4"/>
       <c r="M24" s="1"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="3"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4"/>
       <c r="M25" s="1"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="3"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="4"/>
       <c r="M26" s="1"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="3"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="4"/>
       <c r="M27" s="1"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="3"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="4"/>
       <c r="M28" s="1"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="3"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="4"/>
       <c r="M29" s="1"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="3"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="4"/>
       <c r="M30" s="1"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="3"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="4"/>
       <c r="M31" s="1"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="3"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="4"/>
       <c r="M32" s="1"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="3"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="4"/>
       <c r="M33" s="1"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="3"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="4"/>
       <c r="M34" s="1"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="3"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="4"/>
       <c r="M35" s="1"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="3"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="4"/>
       <c r="M36" s="1"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="3"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="4"/>
       <c r="M37" s="1"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="3"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="4"/>
       <c r="M38" s="1"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="3"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="4"/>
       <c r="M39" s="1"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="3"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4"/>
       <c r="M40" s="1"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="3"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4"/>
       <c r="M41" s="1"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="3"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="4"/>
       <c r="M42" s="1"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="3"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="4"/>
       <c r="M43" s="1"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="3"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="4"/>
       <c r="M44" s="1"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="3"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="4"/>
       <c r="M45" s="1"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="3"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="4"/>
       <c r="M46" s="1"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="3"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="4"/>
       <c r="M47" s="1"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="3"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="4"/>
       <c r="M48" s="1"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="3"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="4"/>
       <c r="M49" s="1"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="3"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="4"/>
       <c r="M50" s="1"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="3"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="4"/>
       <c r="M51" s="1"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="3"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="4"/>
       <c r="M52" s="1"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="3"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="4"/>
       <c r="K53" s="1"/>
       <c r="M53" s="1"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="3"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="4"/>
       <c r="K54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="3"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="4"/>
       <c r="K55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="3"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="3"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="4"/>
       <c r="K56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="3"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="4"/>
       <c r="K57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="3"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="4"/>
       <c r="M58" s="1"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="3"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="4"/>
       <c r="M59" s="1"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="3"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="4"/>
       <c r="K60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="3"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="4"/>
       <c r="K61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="3"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="4"/>
       <c r="K62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="3"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="4"/>
       <c r="K63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="3"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="4"/>
       <c r="K64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="3"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="4"/>
       <c r="K65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1"/>
-      <c r="H66" s="3"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="4"/>
       <c r="K66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G67" s="5"/>
+      <c r="AA67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G68" s="5"/>
+      <c r="AA68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G69" s="5"/>
+      <c r="AA69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G70" s="5"/>
+      <c r="AA70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G71" s="5"/>
+      <c r="AA71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G72" s="5"/>
+      <c r="AA72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G73" s="5"/>
+      <c r="AA73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G74" s="5"/>
+      <c r="AA74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G75" s="5"/>
+      <c r="AA75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G76" s="5"/>
+      <c r="AA76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G77" s="5"/>
+      <c r="AA77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G78" s="5"/>
+      <c r="AA78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G79" s="5"/>
+      <c r="AA79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G80" s="5"/>
+      <c r="AA80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G81" s="5"/>
+      <c r="AA81" s="4"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G82" s="5"/>
+      <c r="AA82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G83" s="5"/>
+      <c r="AA83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G84" s="5"/>
+      <c r="AA84" s="4"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G85" s="5"/>
+      <c r="AA85" s="4"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G86" s="5"/>
+      <c r="AA86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G87" s="5"/>
+      <c r="AA87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G88" s="5"/>
+      <c r="AA88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G89" s="5"/>
+      <c r="AA89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G90" s="5"/>
+      <c r="AA90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G91" s="5"/>
+      <c r="AA91" s="4"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G92" s="5"/>
+      <c r="AA92" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G93" s="5"/>
+      <c r="AA93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G94" s="5"/>
+      <c r="AA94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G95" s="5"/>
+      <c r="AA95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G96" s="5"/>
+      <c r="AA96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G97" s="5"/>
+      <c r="AA97" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G98" s="5"/>
+      <c r="AA98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G99" s="5"/>
+      <c r="AA99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G100" s="5"/>
+      <c r="AA100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G101" s="5"/>
+      <c r="AA101" s="4"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G102" s="5"/>
+      <c r="AA102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G103" s="5"/>
+      <c r="AA103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G104" s="5"/>
+      <c r="AA104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G105" s="5"/>
+      <c r="AA105" s="4"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G106" s="5"/>
+      <c r="AA106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G107" s="5"/>
+      <c r="AA107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G108" s="5"/>
+      <c r="AA108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G109" s="5"/>
+      <c r="AA109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G110" s="5"/>
+      <c r="AA110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G111" s="5"/>
+      <c r="AA111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G112" s="5"/>
+      <c r="AA112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G113" s="5"/>
+      <c r="AA113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G114" s="5"/>
+      <c r="AA114" s="4"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G115" s="5"/>
+      <c r="AA115" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G116" s="5"/>
+      <c r="AA116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G117" s="5"/>
+      <c r="AA117" s="4"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G118" s="5"/>
+      <c r="AA118" s="4"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G119" s="5"/>
+      <c r="AA119" s="4"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G120" s="5"/>
+      <c r="AA120" s="4"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G121" s="5"/>
+      <c r="AA121" s="4"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G122" s="5"/>
+      <c r="AA122" s="4"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G123" s="5"/>
+      <c r="AA123" s="4"/>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G124" s="5"/>
+      <c r="AA124" s="4"/>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G125" s="5"/>
+      <c r="AA125" s="4"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G126" s="5"/>
+      <c r="AA126" s="4"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G127" s="5"/>
+      <c r="AA127" s="4"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G128" s="5"/>
+      <c r="AA128" s="4"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G129" s="5"/>
+      <c r="AA129" s="4"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G130" s="5"/>
+      <c r="AA130" s="4"/>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G131" s="5"/>
+      <c r="AA131" s="4"/>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G132" s="5"/>
+      <c r="AA132" s="4"/>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G133" s="5"/>
+      <c r="AA133" s="4"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G134" s="5"/>
+      <c r="AA134" s="4"/>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G135" s="5"/>
+      <c r="AA135" s="4"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G136" s="5"/>
+      <c r="AA136" s="4"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G137" s="5"/>
+      <c r="AA137" s="4"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G138" s="5"/>
+      <c r="AA138" s="4"/>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G139" s="5"/>
+      <c r="AA139" s="4"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G140" s="5"/>
+      <c r="AA140" s="4"/>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G141" s="5"/>
+      <c r="AA141" s="4"/>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G142" s="5"/>
+      <c r="AA142" s="4"/>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G143" s="5"/>
+      <c r="AA143" s="4"/>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G144" s="5"/>
+      <c r="AA144" s="4"/>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G145" s="5"/>
+      <c r="AA145" s="4"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G146" s="5"/>
+      <c r="AA146" s="4"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G147" s="5"/>
+      <c r="AA147" s="4"/>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G148" s="5"/>
+      <c r="AA148" s="4"/>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G149" s="5"/>
+      <c r="AA149" s="4"/>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G150" s="5"/>
+      <c r="AA150" s="4"/>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G151" s="5"/>
+      <c r="AA151" s="4"/>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G152" s="5"/>
+      <c r="AA152" s="4"/>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G153" s="5"/>
+      <c r="AA153" s="4"/>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G154" s="5"/>
+      <c r="AA154" s="4"/>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G155" s="5"/>
+      <c r="AA155" s="4"/>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G156" s="5"/>
+      <c r="AA156" s="4"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G157" s="5"/>
+      <c r="AA157" s="4"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G158" s="5"/>
+      <c r="AA158" s="4"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G159" s="5"/>
+      <c r="AA159" s="4"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G160" s="5"/>
+      <c r="AA160" s="4"/>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G161" s="5"/>
+      <c r="AA161" s="4"/>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G162" s="5"/>
+      <c r="AA162" s="4"/>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G163" s="5"/>
+      <c r="AA163" s="4"/>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G164" s="5"/>
+      <c r="AA164" s="4"/>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G165" s="5"/>
+      <c r="AA165" s="4"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G166" s="5"/>
+      <c r="AA166" s="4"/>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G167" s="5"/>
+      <c r="AA167" s="4"/>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G168" s="5"/>
+      <c r="AA168" s="4"/>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G169" s="5"/>
+      <c r="AA169" s="4"/>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G170" s="5"/>
+      <c r="AA170" s="4"/>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G171" s="5"/>
+      <c r="AA171" s="4"/>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G172" s="5"/>
+      <c r="AA172" s="4"/>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G173" s="5"/>
+      <c r="AA173" s="4"/>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G174" s="5"/>
+      <c r="AA174" s="4"/>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G175" s="5"/>
+      <c r="AA175" s="4"/>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G176" s="5"/>
+      <c r="AA176" s="4"/>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G177" s="5"/>
+      <c r="AA177" s="4"/>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G178" s="5"/>
+      <c r="AA178" s="4"/>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G179" s="5"/>
+      <c r="AA179" s="4"/>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G180" s="5"/>
+      <c r="AA180" s="4"/>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G181" s="5"/>
+      <c r="AA181" s="4"/>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G182" s="5"/>
+      <c r="AA182" s="4"/>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G183" s="5"/>
+      <c r="AA183" s="4"/>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G184" s="5"/>
+      <c r="AA184" s="4"/>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G185" s="5"/>
+      <c r="AA185" s="4"/>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G186" s="5"/>
+      <c r="AA186" s="4"/>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G187" s="5"/>
+      <c r="AA187" s="4"/>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G188" s="5"/>
+      <c r="AA188" s="4"/>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G189" s="5"/>
+      <c r="AA189" s="4"/>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G190" s="5"/>
+      <c r="AA190" s="4"/>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G191" s="5"/>
+      <c r="AA191" s="4"/>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G192" s="5"/>
+      <c r="AA192" s="4"/>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G193" s="5"/>
+      <c r="AA193" s="4"/>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G194" s="5"/>
+      <c r="AA194" s="4"/>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G195" s="5"/>
+      <c r="AA195" s="4"/>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G196" s="5"/>
+      <c r="AA196" s="4"/>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G197" s="5"/>
+      <c r="AA197" s="4"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G198" s="5"/>
+      <c r="AA198" s="4"/>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G199" s="5"/>
+      <c r="AA199" s="4"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G200" s="5"/>
+      <c r="AA200" s="4"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G201" s="5"/>
+      <c r="AA201" s="4"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G202" s="5"/>
+      <c r="AA202" s="4"/>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G203" s="5"/>
+      <c r="AA203" s="4"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G204" s="5"/>
+      <c r="AA204" s="4"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G205" s="5"/>
+      <c r="AA205" s="4"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G206" s="5"/>
+      <c r="AA206" s="4"/>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G207" s="5"/>
+      <c r="AA207" s="4"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G208" s="5"/>
+      <c r="AA208" s="4"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G209" s="5"/>
+      <c r="AA209" s="4"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G210" s="5"/>
+      <c r="AA210" s="4"/>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G211" s="5"/>
+      <c r="AA211" s="4"/>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G212" s="5"/>
+      <c r="AA212" s="4"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G213" s="5"/>
+      <c r="AA213" s="4"/>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G214" s="5"/>
+      <c r="AA214" s="4"/>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G215" s="5"/>
+      <c r="AA215" s="4"/>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G216" s="5"/>
+      <c r="AA216" s="4"/>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G217" s="5"/>
+      <c r="AA217" s="4"/>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G218" s="5"/>
+      <c r="AA218" s="4"/>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G219" s="5"/>
+      <c r="AA219" s="4"/>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G220" s="5"/>
+      <c r="AA220" s="4"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G221" s="5"/>
+      <c r="AA221" s="4"/>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G222" s="5"/>
+      <c r="AA222" s="4"/>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G223" s="5"/>
+      <c r="AA223" s="4"/>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G224" s="5"/>
+      <c r="AA224" s="4"/>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G225" s="5"/>
+      <c r="AA225" s="4"/>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G226" s="5"/>
+      <c r="AA226" s="4"/>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G227" s="5"/>
+      <c r="AA227" s="4"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G228" s="5"/>
+      <c r="AA228" s="4"/>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G229" s="5"/>
+      <c r="AA229" s="4"/>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G230" s="5"/>
+      <c r="AA230" s="4"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G231" s="5"/>
+      <c r="AA231" s="4"/>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G232" s="5"/>
+      <c r="AA232" s="4"/>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G233" s="5"/>
+      <c r="AA233" s="4"/>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G234" s="5"/>
+      <c r="AA234" s="4"/>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G235" s="5"/>
+      <c r="AA235" s="4"/>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G236" s="5"/>
+      <c r="AA236" s="4"/>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G237" s="5"/>
+      <c r="AA237" s="4"/>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G238" s="5"/>
+      <c r="AA238" s="4"/>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G239" s="5"/>
+      <c r="AA239" s="4"/>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G240" s="5"/>
+      <c r="AA240" s="4"/>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G241" s="5"/>
+      <c r="AA241" s="4"/>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G242" s="5"/>
+      <c r="AA242" s="4"/>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G243" s="5"/>
+      <c r="AA243" s="4"/>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G244" s="5"/>
+      <c r="AA244" s="4"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G245" s="5"/>
+      <c r="AA245" s="4"/>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G246" s="5"/>
+      <c r="AA246" s="4"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G247" s="5"/>
+      <c r="AA247" s="4"/>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G248" s="5"/>
+      <c r="AA248" s="4"/>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G249" s="5"/>
+      <c r="AA249" s="4"/>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G250" s="5"/>
+      <c r="AA250" s="4"/>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G251" s="5"/>
+      <c r="AA251" s="4"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G252" s="5"/>
+      <c r="AA252" s="4"/>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G253" s="5"/>
+      <c r="AA253" s="4"/>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G254" s="5"/>
+      <c r="AA254" s="4"/>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G255" s="5"/>
+      <c r="AA255" s="4"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G256" s="5"/>
+      <c r="AA256" s="4"/>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G257" s="5"/>
+      <c r="AA257" s="4"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G258" s="5"/>
+      <c r="AA258" s="4"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G259" s="5"/>
+      <c r="AA259" s="4"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G260" s="5"/>
+      <c r="AA260" s="4"/>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G261" s="5"/>
+      <c r="AA261" s="4"/>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G262" s="5"/>
+      <c r="AA262" s="4"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G263" s="5"/>
+      <c r="AA263" s="4"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G264" s="5"/>
+      <c r="AA264" s="4"/>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G265" s="5"/>
+      <c r="AA265" s="4"/>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G266" s="5"/>
+      <c r="AA266" s="4"/>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G267" s="5"/>
+      <c r="AA267" s="4"/>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G268" s="5"/>
+      <c r="AA268" s="4"/>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G269" s="5"/>
+      <c r="AA269" s="4"/>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G270" s="5"/>
+      <c r="AA270" s="4"/>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G271" s="5"/>
+      <c r="AA271" s="4"/>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G272" s="5"/>
+      <c r="AA272" s="4"/>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G273" s="5"/>
+      <c r="AA273" s="4"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G274" s="5"/>
+      <c r="AA274" s="4"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G275" s="5"/>
+      <c r="AA275" s="4"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G276" s="5"/>
+      <c r="AA276" s="4"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G277" s="5"/>
+      <c r="AA277" s="4"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G278" s="5"/>
+      <c r="AA278" s="4"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G279" s="5"/>
+      <c r="AA279" s="4"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G280" s="5"/>
+      <c r="AA280" s="4"/>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G281" s="5"/>
+      <c r="AA281" s="4"/>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G282" s="5"/>
+      <c r="AA282" s="4"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G283" s="5"/>
+      <c r="AA283" s="4"/>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G284" s="5"/>
+      <c r="AA284" s="4"/>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G285" s="5"/>
+      <c r="AA285" s="4"/>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G286" s="5"/>
+      <c r="AA286" s="4"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G287" s="5"/>
+      <c r="AA287" s="4"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G288" s="5"/>
+      <c r="AA288" s="4"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G289" s="5"/>
+      <c r="AA289" s="4"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G290" s="5"/>
+      <c r="AA290" s="4"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G291" s="5"/>
+      <c r="AA291" s="4"/>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G292" s="5"/>
+      <c r="AA292" s="4"/>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G293" s="5"/>
+      <c r="AA293" s="4"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G294" s="5"/>
+      <c r="AA294" s="4"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G295" s="5"/>
+      <c r="AA295" s="4"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G296" s="5"/>
+      <c r="AA296" s="4"/>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G297" s="5"/>
+      <c r="AA297" s="4"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G298" s="5"/>
+      <c r="AA298" s="4"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G299" s="5"/>
+      <c r="AA299" s="4"/>
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G300" s="5"/>
+      <c r="AA300" s="4"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G301" s="5"/>
+      <c r="AA301" s="4"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G302" s="5"/>
+      <c r="AA302" s="4"/>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G303" s="5"/>
+      <c r="AA303" s="4"/>
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G304" s="5"/>
+      <c r="AA304" s="4"/>
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G305" s="5"/>
+      <c r="AA305" s="4"/>
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G306" s="5"/>
+      <c r="AA306" s="4"/>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G307" s="5"/>
+      <c r="AA307" s="4"/>
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G308" s="5"/>
+      <c r="AA308" s="4"/>
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G309" s="5"/>
+      <c r="AA309" s="4"/>
+    </row>
+    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G310" s="5"/>
+      <c r="AA310" s="4"/>
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G311" s="5"/>
+      <c r="AA311" s="4"/>
+    </row>
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G312" s="5"/>
+      <c r="AA312" s="4"/>
+    </row>
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G313" s="5"/>
+      <c r="AA313" s="4"/>
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G314" s="5"/>
+      <c r="AA314" s="4"/>
+    </row>
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G315" s="5"/>
+      <c r="AA315" s="4"/>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G316" s="5"/>
+      <c r="AA316" s="4"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G317" s="5"/>
+      <c r="AA317" s="4"/>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G318" s="5"/>
+      <c r="AA318" s="4"/>
+    </row>
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G319" s="5"/>
+      <c r="AA319" s="4"/>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G320" s="5"/>
+      <c r="AA320" s="4"/>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G321" s="5"/>
+      <c r="AA321" s="4"/>
+    </row>
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G322" s="5"/>
+      <c r="AA322" s="4"/>
+    </row>
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G323" s="5"/>
+      <c r="AA323" s="4"/>
+    </row>
+    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G324" s="5"/>
+      <c r="AA324" s="4"/>
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G325" s="5"/>
+      <c r="AA325" s="4"/>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G326" s="5"/>
+      <c r="AA326" s="4"/>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G327" s="5"/>
+      <c r="AA327" s="4"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G328" s="5"/>
+      <c r="AA328" s="4"/>
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G329" s="5"/>
+      <c r="AA329" s="4"/>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G330" s="5"/>
+      <c r="AA330" s="4"/>
+    </row>
+    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G331" s="5"/>
+      <c r="AA331" s="4"/>
+    </row>
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G332" s="5"/>
+      <c r="AA332" s="4"/>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G333" s="5"/>
+      <c r="AA333" s="4"/>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G334" s="5"/>
+      <c r="AA334" s="4"/>
+    </row>
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G335" s="5"/>
+      <c r="AA335" s="4"/>
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G336" s="5"/>
+      <c r="AA336" s="4"/>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G337" s="5"/>
+      <c r="AA337" s="4"/>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G338" s="5"/>
+      <c r="AA338" s="4"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G339" s="5"/>
+      <c r="AA339" s="4"/>
+    </row>
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G340" s="5"/>
+      <c r="AA340" s="4"/>
+    </row>
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G341" s="5"/>
+      <c r="AA341" s="4"/>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G342" s="5"/>
+      <c r="AA342" s="4"/>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G343" s="5"/>
+      <c r="AA343" s="4"/>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G344" s="5"/>
+      <c r="AA344" s="4"/>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G345" s="5"/>
+      <c r="AA345" s="4"/>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G346" s="5"/>
+      <c r="AA346" s="4"/>
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G347" s="5"/>
+      <c r="AA347" s="4"/>
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G348" s="5"/>
+      <c r="AA348" s="4"/>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G349" s="5"/>
+      <c r="AA349" s="4"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G350" s="5"/>
+      <c r="AA350" s="4"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G351" s="5"/>
+      <c r="AA351" s="4"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G352" s="5"/>
+      <c r="AA352" s="4"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G353" s="5"/>
+      <c r="AA353" s="4"/>
+    </row>
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G354" s="5"/>
+      <c r="AA354" s="4"/>
+    </row>
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G355" s="5"/>
+      <c r="AA355" s="4"/>
+    </row>
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G356" s="5"/>
+      <c r="AA356" s="4"/>
+    </row>
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G357" s="5"/>
+      <c r="AA357" s="4"/>
+    </row>
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G358" s="5"/>
+      <c r="AA358" s="4"/>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G359" s="5"/>
+      <c r="AA359" s="4"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G360" s="5"/>
+      <c r="AA360" s="4"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G361" s="5"/>
+      <c r="AA361" s="4"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G362" s="5"/>
+      <c r="AA362" s="4"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G363" s="5"/>
+      <c r="AA363" s="4"/>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G364" s="5"/>
+      <c r="AA364" s="4"/>
+    </row>
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G365" s="5"/>
+      <c r="AA365" s="4"/>
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G366" s="5"/>
+      <c r="AA366" s="4"/>
+    </row>
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G367" s="5"/>
+      <c r="AA367" s="4"/>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G368" s="5"/>
+      <c r="AA368" s="4"/>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G369" s="5"/>
+      <c r="AA369" s="4"/>
+    </row>
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G370" s="5"/>
+      <c r="AA370" s="4"/>
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G371" s="5"/>
+      <c r="AA371" s="4"/>
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G372" s="5"/>
+      <c r="AA372" s="4"/>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G373" s="5"/>
+      <c r="AA373" s="4"/>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G374" s="5"/>
+      <c r="AA374" s="4"/>
+    </row>
+    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G375" s="5"/>
+      <c r="AA375" s="4"/>
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G376" s="5"/>
+      <c r="AA376" s="4"/>
+    </row>
+    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G377" s="5"/>
+      <c r="AA377" s="4"/>
+    </row>
+    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G378" s="5"/>
+      <c r="AA378" s="4"/>
+    </row>
+    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G379" s="5"/>
+      <c r="AA379" s="4"/>
+    </row>
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G380" s="5"/>
+      <c r="AA380" s="4"/>
+    </row>
+    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G381" s="5"/>
+      <c r="AA381" s="4"/>
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G382" s="5"/>
+      <c r="AA382" s="4"/>
+    </row>
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G383" s="5"/>
+      <c r="AA383" s="4"/>
+    </row>
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G384" s="5"/>
+      <c r="AA384" s="4"/>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G385" s="5"/>
+      <c r="AA385" s="4"/>
+    </row>
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G386" s="5"/>
+      <c r="AA386" s="4"/>
+    </row>
+    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G387" s="5"/>
+      <c r="AA387" s="4"/>
+    </row>
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G388" s="5"/>
+      <c r="AA388" s="4"/>
+    </row>
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G389" s="5"/>
+      <c r="AA389" s="4"/>
+    </row>
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G390" s="5"/>
+      <c r="AA390" s="4"/>
+    </row>
+    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G391" s="5"/>
+      <c r="AA391" s="4"/>
+    </row>
+    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G392" s="5"/>
+      <c r="AA392" s="4"/>
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G393" s="5"/>
+      <c r="AA393" s="4"/>
+    </row>
+    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G394" s="5"/>
+      <c r="AA394" s="4"/>
+    </row>
+    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G395" s="5"/>
+      <c r="AA395" s="4"/>
+    </row>
+    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G396" s="5"/>
+      <c r="AA396" s="4"/>
+    </row>
+    <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G397" s="5"/>
+      <c r="AA397" s="4"/>
+    </row>
+    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G398" s="5"/>
+      <c r="AA398" s="4"/>
+    </row>
+    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G399" s="5"/>
+      <c r="AA399" s="4"/>
+    </row>
+    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G400" s="5"/>
+      <c r="AA400" s="4"/>
+    </row>
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G401" s="5"/>
+      <c r="AA401" s="4"/>
+    </row>
+    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G402" s="5"/>
+      <c r="AA402" s="4"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G403" s="5"/>
+      <c r="AA403" s="4"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G404" s="5"/>
+      <c r="AA404" s="4"/>
+    </row>
+    <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G405" s="5"/>
+      <c r="AA405" s="4"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G406" s="5"/>
+      <c r="AA406" s="4"/>
+    </row>
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G407" s="5"/>
+      <c r="AA407" s="4"/>
+    </row>
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G408" s="5"/>
+      <c r="AA408" s="4"/>
+    </row>
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G409" s="5"/>
+      <c r="AA409" s="4"/>
+    </row>
+    <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G410" s="5"/>
+      <c r="AA410" s="4"/>
+    </row>
+    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G411" s="5"/>
+      <c r="AA411" s="4"/>
+    </row>
+    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G412" s="5"/>
+      <c r="AA412" s="4"/>
+    </row>
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G413" s="5"/>
+      <c r="AA413" s="4"/>
+    </row>
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G414" s="5"/>
+      <c r="AA414" s="4"/>
+    </row>
+    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G415" s="5"/>
+      <c r="AA415" s="4"/>
+    </row>
+    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G416" s="5"/>
+      <c r="AA416" s="4"/>
+    </row>
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G417" s="5"/>
+      <c r="AA417" s="4"/>
+    </row>
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G418" s="5"/>
+      <c r="AA418" s="4"/>
+    </row>
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G419" s="5"/>
+      <c r="AA419" s="4"/>
+    </row>
+    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G420" s="5"/>
+      <c r="AA420" s="4"/>
+    </row>
+    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G421" s="5"/>
+      <c r="AA421" s="4"/>
+    </row>
+    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G422" s="5"/>
+      <c r="AA422" s="4"/>
+    </row>
+    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G423" s="5"/>
+      <c r="AA423" s="4"/>
+    </row>
+    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G424" s="5"/>
+      <c r="AA424" s="4"/>
+    </row>
+    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G425" s="5"/>
+      <c r="AA425" s="4"/>
+    </row>
+    <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G426" s="5"/>
+      <c r="AA426" s="4"/>
+    </row>
+    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G427" s="5"/>
+      <c r="AA427" s="4"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G428" s="5"/>
+      <c r="AA428" s="4"/>
+    </row>
+    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G429" s="5"/>
+      <c r="AA429" s="4"/>
+    </row>
+    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G430" s="5"/>
+      <c r="AA430" s="4"/>
+    </row>
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G431" s="5"/>
+      <c r="AA431" s="4"/>
+    </row>
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G432" s="5"/>
+      <c r="AA432" s="4"/>
+    </row>
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G433" s="5"/>
+      <c r="AA433" s="4"/>
+    </row>
+    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G434" s="5"/>
+      <c r="AA434" s="4"/>
+    </row>
+    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G435" s="5"/>
+      <c r="AA435" s="4"/>
+    </row>
+    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G436" s="5"/>
+      <c r="AA436" s="4"/>
+    </row>
+    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G437" s="5"/>
+      <c r="AA437" s="4"/>
+    </row>
+    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G438" s="5"/>
+      <c r="AA438" s="4"/>
+    </row>
+    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G439" s="5"/>
+      <c r="AA439" s="4"/>
+    </row>
+    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G440" s="5"/>
+      <c r="AA440" s="4"/>
+    </row>
+    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G441" s="5"/>
+      <c r="AA441" s="4"/>
+    </row>
+    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G442" s="5"/>
+      <c r="AA442" s="4"/>
+    </row>
+    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G443" s="5"/>
+      <c r="AA443" s="4"/>
+    </row>
+    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G444" s="5"/>
+      <c r="AA444" s="4"/>
+    </row>
+    <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G445" s="5"/>
+      <c r="AA445" s="4"/>
+    </row>
+    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G446" s="5"/>
+      <c r="AA446" s="4"/>
+    </row>
+    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G447" s="5"/>
+      <c r="AA447" s="4"/>
+    </row>
+    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G448" s="5"/>
+      <c r="AA448" s="4"/>
+    </row>
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G449" s="5"/>
+      <c r="AA449" s="4"/>
+    </row>
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G450" s="5"/>
+      <c r="AA450" s="4"/>
+    </row>
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G451" s="5"/>
+      <c r="AA451" s="4"/>
+    </row>
+    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G452" s="5"/>
+      <c r="AA452" s="4"/>
+    </row>
+    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G453" s="5"/>
+      <c r="AA453" s="4"/>
+    </row>
+    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G454" s="5"/>
+      <c r="AA454" s="4"/>
+    </row>
+    <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G455" s="5"/>
+      <c r="AA455" s="4"/>
+    </row>
+    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G456" s="5"/>
+      <c r="AA456" s="4"/>
+    </row>
+    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G457" s="5"/>
+      <c r="AA457" s="4"/>
+    </row>
+    <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G458" s="5"/>
+      <c r="AA458" s="4"/>
+    </row>
+    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G459" s="5"/>
+      <c r="AA459" s="4"/>
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G460" s="5"/>
+      <c r="AA460" s="4"/>
+    </row>
+    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G461" s="5"/>
+      <c r="AA461" s="4"/>
+    </row>
+    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G462" s="5"/>
+      <c r="AA462" s="4"/>
+    </row>
+    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G463" s="5"/>
+      <c r="AA463" s="4"/>
+    </row>
+    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G464" s="5"/>
+      <c r="AA464" s="4"/>
+    </row>
+    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G465" s="5"/>
+      <c r="AA465" s="4"/>
+    </row>
+    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G466" s="5"/>
+      <c r="AA466" s="4"/>
+    </row>
+    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G467" s="5"/>
+      <c r="AA467" s="4"/>
+    </row>
+    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G468" s="5"/>
+      <c r="AA468" s="4"/>
+    </row>
+    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G469" s="5"/>
+      <c r="AA469" s="4"/>
+    </row>
+    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G470" s="5"/>
+      <c r="AA470" s="4"/>
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G471" s="5"/>
+      <c r="AA471" s="4"/>
+    </row>
+    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G472" s="5"/>
+      <c r="AA472" s="4"/>
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G473" s="5"/>
+      <c r="AA473" s="4"/>
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G474" s="5"/>
+      <c r="AA474" s="4"/>
+    </row>
+    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G475" s="5"/>
+      <c r="AA475" s="4"/>
+    </row>
+    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G476" s="5"/>
+      <c r="AA476" s="4"/>
+    </row>
+    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G477" s="5"/>
+      <c r="AA477" s="4"/>
+    </row>
+    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G478" s="5"/>
+      <c r="AA478" s="4"/>
+    </row>
+    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G479" s="5"/>
+      <c r="AA479" s="4"/>
+    </row>
+    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G480" s="5"/>
+      <c r="AA480" s="4"/>
+    </row>
+    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G481" s="5"/>
+      <c r="AA481" s="4"/>
+    </row>
+    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G482" s="5"/>
+      <c r="AA482" s="4"/>
+    </row>
+    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G483" s="5"/>
+      <c r="AA483" s="4"/>
+    </row>
+    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G484" s="5"/>
+      <c r="AA484" s="4"/>
+    </row>
+    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G485" s="5"/>
+      <c r="AA485" s="4"/>
+    </row>
+    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G486" s="5"/>
+      <c r="AA486" s="4"/>
+    </row>
+    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G487" s="5"/>
+      <c r="AA487" s="4"/>
+    </row>
+    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G488" s="5"/>
+      <c r="AA488" s="4"/>
+    </row>
+    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G489" s="5"/>
+      <c r="AA489" s="4"/>
+    </row>
+    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G490" s="5"/>
+      <c r="AA490" s="4"/>
+    </row>
+    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G491" s="5"/>
+      <c r="AA491" s="4"/>
+    </row>
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G492" s="5"/>
+      <c r="AA492" s="4"/>
+    </row>
+    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G493" s="5"/>
+      <c r="AA493" s="4"/>
+    </row>
+    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G494" s="5"/>
+      <c r="AA494" s="4"/>
+    </row>
+    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G495" s="5"/>
+      <c r="AA495" s="4"/>
+    </row>
+    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G496" s="5"/>
+      <c r="AA496" s="4"/>
+    </row>
+    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G497" s="5"/>
+      <c r="AA497" s="4"/>
+    </row>
+    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G498" s="5"/>
+      <c r="AA498" s="4"/>
+    </row>
+    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G499" s="5"/>
+      <c r="AA499" s="4"/>
+    </row>
+    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G500" s="5"/>
+      <c r="AA500" s="4"/>
+    </row>
+    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G501" s="5"/>
+      <c r="AA501" s="4"/>
+    </row>
+    <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G502" s="5"/>
+      <c r="AA502" s="4"/>
+    </row>
+    <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G503" s="5"/>
+      <c r="AA503" s="4"/>
+    </row>
+    <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G504" s="5"/>
+      <c r="AA504" s="4"/>
+    </row>
+    <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G505" s="5"/>
+      <c r="AA505" s="4"/>
+    </row>
+    <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G506" s="5"/>
+      <c r="AA506" s="4"/>
+    </row>
+    <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G507" s="5"/>
+      <c r="AA507" s="4"/>
+    </row>
+    <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G508" s="5"/>
+      <c r="AA508" s="4"/>
+    </row>
+    <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G509" s="5"/>
+      <c r="AA509" s="4"/>
+    </row>
+    <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G510" s="5"/>
+      <c r="AA510" s="4"/>
+    </row>
+    <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G511" s="5"/>
+      <c r="AA511" s="4"/>
+    </row>
+    <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G512" s="5"/>
+      <c r="AA512" s="4"/>
+    </row>
+    <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G513" s="5"/>
+      <c r="AA513" s="4"/>
+    </row>
+    <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G514" s="5"/>
+      <c r="AA514" s="4"/>
+    </row>
+    <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G515" s="5"/>
+      <c r="AA515" s="4"/>
+    </row>
+    <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G516" s="5"/>
+      <c r="AA516" s="4"/>
+    </row>
+    <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G517" s="5"/>
+      <c r="AA517" s="4"/>
+    </row>
+    <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G518" s="5"/>
+      <c r="AA518" s="4"/>
+    </row>
+    <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G519" s="5"/>
+      <c r="AA519" s="4"/>
+    </row>
+    <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G520" s="5"/>
+      <c r="AA520" s="4"/>
+    </row>
+    <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G521" s="5"/>
+      <c r="AA521" s="4"/>
+    </row>
+    <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G522" s="5"/>
+      <c r="AA522" s="4"/>
+    </row>
+    <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G523" s="5"/>
+      <c r="AA523" s="4"/>
+    </row>
+    <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G524" s="5"/>
+      <c r="AA524" s="4"/>
+    </row>
+    <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G525" s="5"/>
+      <c r="AA525" s="4"/>
+    </row>
+    <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G526" s="5"/>
+      <c r="AA526" s="4"/>
+    </row>
+    <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G527" s="5"/>
+      <c r="AA527" s="4"/>
+    </row>
+    <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G528" s="5"/>
+      <c r="AA528" s="4"/>
+    </row>
+    <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G529" s="5"/>
+      <c r="AA529" s="4"/>
+    </row>
+    <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G530" s="5"/>
+      <c r="AA530" s="4"/>
+    </row>
+    <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G531" s="5"/>
+      <c r="AA531" s="4"/>
+    </row>
+    <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G532" s="5"/>
+      <c r="AA532" s="4"/>
+    </row>
+    <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G533" s="5"/>
+      <c r="AA533" s="4"/>
+    </row>
+    <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G534" s="5"/>
+      <c r="AA534" s="4"/>
+    </row>
+    <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G535" s="5"/>
+      <c r="AA535" s="4"/>
+    </row>
+    <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G536" s="5"/>
+      <c r="AA536" s="4"/>
+    </row>
+    <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G537" s="5"/>
+      <c r="AA537" s="4"/>
+    </row>
+    <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G538" s="5"/>
+      <c r="AA538" s="4"/>
+    </row>
+    <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G539" s="5"/>
+      <c r="AA539" s="4"/>
+    </row>
+    <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G540" s="5"/>
+      <c r="AA540" s="4"/>
+    </row>
+    <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G541" s="5"/>
+      <c r="AA541" s="4"/>
+    </row>
+    <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G542" s="5"/>
+      <c r="AA542" s="4"/>
+    </row>
+    <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G543" s="5"/>
+      <c r="AA543" s="4"/>
+    </row>
+    <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G544" s="5"/>
+      <c r="AA544" s="4"/>
+    </row>
+    <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G545" s="5"/>
+      <c r="AA545" s="4"/>
+    </row>
+    <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G546" s="5"/>
+      <c r="AA546" s="4"/>
+    </row>
+    <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G547" s="5"/>
+      <c r="AA547" s="4"/>
+    </row>
+    <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G548" s="5"/>
+      <c r="AA548" s="4"/>
+    </row>
+    <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G549" s="5"/>
+      <c r="AA549" s="4"/>
+    </row>
+    <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G550" s="5"/>
+      <c r="AA550" s="4"/>
+    </row>
+    <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G551" s="5"/>
+      <c r="AA551" s="4"/>
+    </row>
+    <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G552" s="5"/>
+      <c r="AA552" s="4"/>
+    </row>
+    <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G553" s="5"/>
+      <c r="AA553" s="4"/>
+    </row>
+    <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G554" s="5"/>
+      <c r="AA554" s="4"/>
+    </row>
+    <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G555" s="5"/>
+      <c r="AA555" s="4"/>
+    </row>
+    <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G556" s="5"/>
+      <c r="AA556" s="4"/>
+    </row>
+    <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G557" s="5"/>
+      <c r="AA557" s="4"/>
+    </row>
+    <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G558" s="5"/>
+      <c r="AA558" s="4"/>
+    </row>
+    <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G559" s="5"/>
+      <c r="AA559" s="4"/>
+    </row>
+    <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G560" s="5"/>
+      <c r="AA560" s="4"/>
+    </row>
+    <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G561" s="5"/>
+      <c r="AA561" s="4"/>
+    </row>
+    <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G562" s="5"/>
+      <c r="AA562" s="4"/>
+    </row>
+    <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G563" s="5"/>
+      <c r="AA563" s="4"/>
+    </row>
+    <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G564" s="5"/>
+      <c r="AA564" s="4"/>
+    </row>
+    <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G565" s="5"/>
+      <c r="AA565" s="4"/>
+    </row>
+    <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G566" s="5"/>
+      <c r="AA566" s="4"/>
+    </row>
+    <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G567" s="5"/>
+      <c r="AA567" s="4"/>
+    </row>
+    <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G568" s="5"/>
+      <c r="AA568" s="4"/>
+    </row>
+    <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G569" s="5"/>
+      <c r="AA569" s="4"/>
+    </row>
+    <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G570" s="5"/>
+      <c r="AA570" s="4"/>
+    </row>
+    <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G571" s="5"/>
+      <c r="AA571" s="4"/>
+    </row>
+    <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G572" s="5"/>
+      <c r="AA572" s="4"/>
+    </row>
+    <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G573" s="5"/>
+      <c r="AA573" s="4"/>
+    </row>
+    <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G574" s="5"/>
+      <c r="AA574" s="4"/>
+    </row>
+    <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G575" s="5"/>
+      <c r="AA575" s="4"/>
+    </row>
+    <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G576" s="5"/>
+      <c r="AA576" s="4"/>
+    </row>
+    <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G577" s="5"/>
+      <c r="AA577" s="4"/>
+    </row>
+    <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G578" s="5"/>
+      <c r="AA578" s="4"/>
+    </row>
+    <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G579" s="5"/>
+      <c r="AA579" s="4"/>
+    </row>
+    <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G580" s="5"/>
+      <c r="AA580" s="4"/>
+    </row>
+    <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G581" s="5"/>
+      <c r="AA581" s="4"/>
+    </row>
+    <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G582" s="5"/>
+      <c r="AA582" s="4"/>
+    </row>
+    <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G583" s="5"/>
+      <c r="AA583" s="4"/>
+    </row>
+    <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G584" s="5"/>
+      <c r="AA584" s="4"/>
+    </row>
+    <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G585" s="5"/>
+      <c r="AA585" s="4"/>
+    </row>
+    <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G586" s="5"/>
+      <c r="AA586" s="4"/>
+    </row>
+    <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G587" s="5"/>
+      <c r="AA587" s="4"/>
+    </row>
+    <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G588" s="5"/>
+      <c r="AA588" s="4"/>
+    </row>
+    <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G589" s="5"/>
+      <c r="AA589" s="4"/>
+    </row>
+    <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G590" s="5"/>
+      <c r="AA590" s="4"/>
+    </row>
+    <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G591" s="5"/>
+      <c r="AA591" s="4"/>
+    </row>
+    <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G592" s="5"/>
+      <c r="AA592" s="4"/>
+    </row>
+    <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G593" s="5"/>
+      <c r="AA593" s="4"/>
+    </row>
+    <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G594" s="5"/>
+      <c r="AA594" s="4"/>
+    </row>
+    <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G595" s="5"/>
+      <c r="AA595" s="4"/>
+    </row>
+    <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G596" s="5"/>
+      <c r="AA596" s="4"/>
+    </row>
+    <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G597" s="5"/>
+      <c r="AA597" s="4"/>
+    </row>
+    <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G598" s="5"/>
+      <c r="AA598" s="4"/>
+    </row>
+    <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G599" s="5"/>
+      <c r="AA599" s="4"/>
+    </row>
+    <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G600" s="5"/>
+      <c r="AA600" s="4"/>
+    </row>
+    <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G601" s="5"/>
+      <c r="AA601" s="4"/>
+    </row>
+    <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G602" s="5"/>
+      <c r="AA602" s="4"/>
+    </row>
+    <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G603" s="5"/>
+      <c r="AA603" s="4"/>
+    </row>
+    <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G604" s="5"/>
+      <c r="AA604" s="4"/>
+    </row>
+    <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G605" s="5"/>
+      <c r="AA605" s="4"/>
+    </row>
+    <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G606" s="5"/>
+      <c r="AA606" s="4"/>
+    </row>
+    <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G607" s="5"/>
+      <c r="AA607" s="4"/>
+    </row>
+    <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G608" s="5"/>
+      <c r="AA608" s="4"/>
+    </row>
+    <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G609" s="5"/>
+      <c r="AA609" s="4"/>
+    </row>
+    <row r="610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G610" s="5"/>
+      <c r="AA610" s="4"/>
+    </row>
+    <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G611" s="5"/>
+      <c r="AA611" s="4"/>
+    </row>
+    <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G612" s="5"/>
+      <c r="AA612" s="4"/>
+    </row>
+    <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G613" s="5"/>
+      <c r="AA613" s="4"/>
+    </row>
+    <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G614" s="5"/>
+      <c r="AA614" s="4"/>
+    </row>
+    <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G615" s="5"/>
+      <c r="AA615" s="4"/>
+    </row>
+    <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G616" s="5"/>
+      <c r="AA616" s="4"/>
+    </row>
+    <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G617" s="5"/>
+      <c r="AA617" s="4"/>
+    </row>
+    <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G618" s="5"/>
+      <c r="AA618" s="4"/>
+    </row>
+    <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G619" s="5"/>
+      <c r="AA619" s="4"/>
+    </row>
+    <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G620" s="5"/>
+      <c r="AA620" s="4"/>
+    </row>
+    <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G621" s="5"/>
+      <c r="AA621" s="4"/>
+    </row>
+    <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G622" s="5"/>
+      <c r="AA622" s="4"/>
+    </row>
+    <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G623" s="5"/>
+      <c r="AA623" s="4"/>
+    </row>
+    <row r="624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G624" s="5"/>
+      <c r="AA624" s="4"/>
+    </row>
+    <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G625" s="5"/>
+      <c r="AA625" s="4"/>
+    </row>
+    <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G626" s="5"/>
+      <c r="AA626" s="4"/>
+    </row>
+    <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G627" s="5"/>
+      <c r="AA627" s="4"/>
+    </row>
+    <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G628" s="5"/>
+      <c r="AA628" s="4"/>
+    </row>
+    <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G629" s="5"/>
+      <c r="AA629" s="4"/>
+    </row>
+    <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G630" s="5"/>
+      <c r="AA630" s="4"/>
+    </row>
+    <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G631" s="5"/>
+      <c r="AA631" s="4"/>
+    </row>
+    <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G632" s="5"/>
+      <c r="AA632" s="4"/>
+    </row>
+    <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G633" s="5"/>
+      <c r="AA633" s="4"/>
+    </row>
+    <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G634" s="5"/>
+      <c r="AA634" s="4"/>
+    </row>
+    <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G635" s="5"/>
+      <c r="AA635" s="4"/>
+    </row>
+    <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G636" s="5"/>
+      <c r="AA636" s="4"/>
+    </row>
+    <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G637" s="5"/>
+      <c r="AA637" s="4"/>
+    </row>
+    <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G638" s="5"/>
+      <c r="AA638" s="4"/>
+    </row>
+    <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G639" s="5"/>
+      <c r="AA639" s="4"/>
+    </row>
+    <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G640" s="5"/>
+      <c r="AA640" s="4"/>
+    </row>
+    <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G641" s="5"/>
+      <c r="AA641" s="4"/>
+    </row>
+    <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G642" s="5"/>
+      <c r="AA642" s="4"/>
+    </row>
+    <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G643" s="5"/>
+      <c r="AA643" s="4"/>
+    </row>
+    <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G644" s="5"/>
+      <c r="AA644" s="4"/>
+    </row>
+    <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G645" s="5"/>
+      <c r="AA645" s="4"/>
+    </row>
+    <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G646" s="5"/>
+      <c r="AA646" s="4"/>
+    </row>
+    <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G647" s="5"/>
+      <c r="AA647" s="4"/>
+    </row>
+    <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G648" s="5"/>
+      <c r="AA648" s="4"/>
+    </row>
+    <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G649" s="5"/>
+      <c r="AA649" s="4"/>
+    </row>
+    <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G650" s="5"/>
+      <c r="AA650" s="4"/>
+    </row>
+    <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G651" s="5"/>
+      <c r="AA651" s="4"/>
+    </row>
+    <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G652" s="5"/>
+      <c r="AA652" s="4"/>
+    </row>
+    <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G653" s="5"/>
+      <c r="AA653" s="4"/>
+    </row>
+    <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G654" s="5"/>
+      <c r="AA654" s="4"/>
+    </row>
+    <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G655" s="5"/>
+      <c r="AA655" s="4"/>
+    </row>
+    <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G656" s="5"/>
+      <c r="AA656" s="4"/>
+    </row>
+    <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G657" s="5"/>
+      <c r="AA657" s="4"/>
+    </row>
+    <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G658" s="5"/>
+      <c r="AA658" s="4"/>
+    </row>
+    <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G659" s="5"/>
+      <c r="AA659" s="4"/>
+    </row>
+    <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G660" s="5"/>
+      <c r="AA660" s="4"/>
+    </row>
+    <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G661" s="5"/>
+      <c r="AA661" s="4"/>
+    </row>
+    <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G662" s="5"/>
+      <c r="AA662" s="4"/>
+    </row>
+    <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G663" s="5"/>
+      <c r="AA663" s="4"/>
+    </row>
+    <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G664" s="5"/>
+      <c r="AA664" s="4"/>
+    </row>
+    <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G665" s="5"/>
+      <c r="AA665" s="4"/>
+    </row>
+    <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G666" s="5"/>
+      <c r="AA666" s="4"/>
+    </row>
+    <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G667" s="5"/>
+      <c r="AA667" s="4"/>
+    </row>
+    <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G668" s="5"/>
+      <c r="AA668" s="4"/>
+    </row>
+    <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G669" s="5"/>
+      <c r="AA669" s="4"/>
+    </row>
+    <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G670" s="5"/>
+      <c r="AA670" s="4"/>
+    </row>
+    <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G671" s="5"/>
+      <c r="AA671" s="4"/>
+    </row>
+    <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G672" s="5"/>
+      <c r="AA672" s="4"/>
+    </row>
+    <row r="673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G673" s="5"/>
+      <c r="AA673" s="4"/>
+    </row>
+    <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G674" s="5"/>
+      <c r="AA674" s="4"/>
+    </row>
+    <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G675" s="5"/>
+      <c r="AA675" s="4"/>
+    </row>
+    <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G676" s="5"/>
+      <c r="AA676" s="4"/>
+    </row>
+    <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G677" s="5"/>
+      <c r="AA677" s="4"/>
+    </row>
+    <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G678" s="5"/>
+      <c r="AA678" s="4"/>
+    </row>
+    <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G679" s="5"/>
+      <c r="AA679" s="4"/>
+    </row>
+    <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G680" s="5"/>
+      <c r="AA680" s="4"/>
+    </row>
+    <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G681" s="5"/>
+      <c r="AA681" s="4"/>
+    </row>
+    <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G682" s="5"/>
+      <c r="AA682" s="4"/>
+    </row>
+    <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G683" s="5"/>
+      <c r="AA683" s="4"/>
+    </row>
+    <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G684" s="5"/>
+      <c r="AA684" s="4"/>
+    </row>
+    <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G685" s="5"/>
+      <c r="AA685" s="4"/>
+    </row>
+    <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G686" s="5"/>
+      <c r="AA686" s="4"/>
+    </row>
+    <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G687" s="5"/>
+      <c r="AA687" s="4"/>
+    </row>
+    <row r="688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G688" s="5"/>
+      <c r="AA688" s="4"/>
+    </row>
+    <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G689" s="5"/>
+      <c r="AA689" s="4"/>
+    </row>
+    <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G690" s="5"/>
+      <c r="AA690" s="4"/>
+    </row>
+    <row r="691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G691" s="5"/>
+      <c r="AA691" s="4"/>
+    </row>
+    <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G692" s="5"/>
+      <c r="AA692" s="4"/>
+    </row>
+    <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G693" s="5"/>
+      <c r="AA693" s="4"/>
+    </row>
+    <row r="694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G694" s="5"/>
+      <c r="AA694" s="4"/>
+    </row>
+    <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G695" s="5"/>
+      <c r="AA695" s="4"/>
+    </row>
+    <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G696" s="5"/>
+      <c r="AA696" s="4"/>
+    </row>
+    <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G697" s="5"/>
+      <c r="AA697" s="4"/>
+    </row>
+    <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G698" s="5"/>
+      <c r="AA698" s="4"/>
+    </row>
+    <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G699" s="5"/>
+      <c r="AA699" s="4"/>
+    </row>
+    <row r="700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G700" s="5"/>
+      <c r="AA700" s="4"/>
+    </row>
+    <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G701" s="5"/>
+      <c r="AA701" s="4"/>
+    </row>
+    <row r="702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G702" s="5"/>
+      <c r="AA702" s="4"/>
+    </row>
+    <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G703" s="5"/>
+      <c r="AA703" s="4"/>
+    </row>
+    <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G704" s="5"/>
+      <c r="AA704" s="4"/>
+    </row>
+    <row r="705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G705" s="5"/>
+      <c r="AA705" s="4"/>
+    </row>
+    <row r="706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G706" s="5"/>
+      <c r="AA706" s="4"/>
+    </row>
+    <row r="707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G707" s="5"/>
+      <c r="AA707" s="4"/>
+    </row>
+    <row r="708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G708" s="5"/>
+      <c r="AA708" s="4"/>
+    </row>
+    <row r="709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G709" s="5"/>
+      <c r="AA709" s="4"/>
+    </row>
+    <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G710" s="5"/>
+      <c r="AA710" s="4"/>
+    </row>
+    <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G711" s="5"/>
+      <c r="AA711" s="4"/>
+    </row>
+    <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G712" s="5"/>
+      <c r="AA712" s="4"/>
+    </row>
+    <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G713" s="5"/>
+      <c r="AA713" s="4"/>
+    </row>
+    <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G714" s="5"/>
+      <c r="AA714" s="4"/>
+    </row>
+    <row r="715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G715" s="5"/>
+      <c r="AA715" s="4"/>
+    </row>
+    <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G716" s="5"/>
+      <c r="AA716" s="4"/>
+    </row>
+    <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G717" s="5"/>
+      <c r="AA717" s="4"/>
+    </row>
+    <row r="718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G718" s="5"/>
+      <c r="AA718" s="4"/>
+    </row>
+    <row r="719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G719" s="5"/>
+      <c r="AA719" s="4"/>
+    </row>
+    <row r="720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G720" s="5"/>
+      <c r="AA720" s="4"/>
+    </row>
+    <row r="721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G721" s="5"/>
+      <c r="AA721" s="4"/>
+    </row>
+    <row r="722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G722" s="5"/>
+      <c r="AA722" s="4"/>
+    </row>
+    <row r="723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G723" s="5"/>
+      <c r="AA723" s="4"/>
+    </row>
+    <row r="724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G724" s="5"/>
+      <c r="AA724" s="4"/>
+    </row>
+    <row r="725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G725" s="5"/>
+      <c r="AA725" s="4"/>
+    </row>
+    <row r="726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G726" s="5"/>
+      <c r="AA726" s="4"/>
+    </row>
+    <row r="727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G727" s="5"/>
+      <c r="AA727" s="4"/>
+    </row>
+    <row r="728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G728" s="5"/>
+      <c r="AA728" s="4"/>
+    </row>
+    <row r="729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G729" s="5"/>
+      <c r="AA729" s="4"/>
+    </row>
+    <row r="730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G730" s="5"/>
+      <c r="AA730" s="4"/>
+    </row>
+    <row r="731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G731" s="5"/>
+      <c r="AA731" s="4"/>
+    </row>
+    <row r="732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G732" s="5"/>
+      <c r="AA732" s="4"/>
+    </row>
+    <row r="733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G733" s="5"/>
+      <c r="AA733" s="4"/>
+    </row>
+    <row r="734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G734" s="5"/>
+      <c r="AA734" s="4"/>
+    </row>
+    <row r="735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G735" s="5"/>
+      <c r="AA735" s="4"/>
+    </row>
+    <row r="736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G736" s="5"/>
+      <c r="AA736" s="4"/>
+    </row>
+    <row r="737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G737" s="5"/>
+      <c r="AA737" s="4"/>
+    </row>
+    <row r="738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G738" s="5"/>
+      <c r="AA738" s="4"/>
+    </row>
+    <row r="739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G739" s="5"/>
+      <c r="AA739" s="4"/>
+    </row>
+    <row r="740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G740" s="5"/>
+      <c r="AA740" s="4"/>
+    </row>
+    <row r="741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G741" s="5"/>
+      <c r="AA741" s="4"/>
+    </row>
+    <row r="742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G742" s="5"/>
+      <c r="AA742" s="4"/>
+    </row>
+    <row r="743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G743" s="5"/>
+      <c r="AA743" s="4"/>
+    </row>
+    <row r="744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G744" s="5"/>
+      <c r="AA744" s="4"/>
+    </row>
+    <row r="745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G745" s="5"/>
+      <c r="AA745" s="4"/>
+    </row>
+    <row r="746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G746" s="5"/>
+      <c r="AA746" s="4"/>
+    </row>
+    <row r="747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G747" s="5"/>
+      <c r="AA747" s="4"/>
+    </row>
+    <row r="748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G748" s="5"/>
+      <c r="AA748" s="4"/>
+    </row>
+    <row r="749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G749" s="5"/>
+      <c r="AA749" s="4"/>
+    </row>
+    <row r="750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G750" s="5"/>
+      <c r="AA750" s="4"/>
+    </row>
+    <row r="751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G751" s="5"/>
+      <c r="AA751" s="4"/>
+    </row>
+    <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G752" s="5"/>
+      <c r="AA752" s="4"/>
+    </row>
+    <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G753" s="5"/>
+      <c r="AA753" s="4"/>
+    </row>
+    <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G754" s="5"/>
+      <c r="AA754" s="4"/>
+    </row>
+    <row r="755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G755" s="5"/>
+      <c r="AA755" s="4"/>
+    </row>
+    <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G756" s="5"/>
+      <c r="AA756" s="4"/>
+    </row>
+    <row r="757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G757" s="5"/>
+      <c r="AA757" s="4"/>
+    </row>
+    <row r="758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G758" s="5"/>
+      <c r="AA758" s="4"/>
+    </row>
+    <row r="759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G759" s="5"/>
+      <c r="AA759" s="4"/>
+    </row>
+    <row r="760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G760" s="5"/>
+      <c r="AA760" s="4"/>
+    </row>
+    <row r="761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G761" s="5"/>
+      <c r="AA761" s="4"/>
+    </row>
+    <row r="762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G762" s="5"/>
+      <c r="AA762" s="4"/>
+    </row>
+    <row r="763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G763" s="5"/>
+      <c r="AA763" s="4"/>
+    </row>
+    <row r="764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G764" s="5"/>
+      <c r="AA764" s="4"/>
+    </row>
+    <row r="765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G765" s="5"/>
+      <c r="AA765" s="4"/>
+    </row>
+    <row r="766" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G766" s="5"/>
+      <c r="AA766" s="4"/>
+    </row>
+    <row r="767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G767" s="5"/>
+      <c r="AA767" s="4"/>
+    </row>
+    <row r="768" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G768" s="5"/>
+      <c r="AA768" s="4"/>
+    </row>
+    <row r="769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G769" s="5"/>
+      <c r="AA769" s="4"/>
+    </row>
+    <row r="770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G770" s="5"/>
+      <c r="AA770" s="4"/>
+    </row>
+    <row r="771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G771" s="5"/>
+      <c r="AA771" s="4"/>
+    </row>
+    <row r="772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G772" s="5"/>
+      <c r="AA772" s="4"/>
+    </row>
+    <row r="773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G773" s="5"/>
+      <c r="AA773" s="4"/>
+    </row>
+    <row r="774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G774" s="5"/>
+      <c r="AA774" s="4"/>
+    </row>
+    <row r="775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G775" s="5"/>
+      <c r="AA775" s="4"/>
+    </row>
+    <row r="776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G776" s="5"/>
+      <c r="AA776" s="4"/>
+    </row>
+    <row r="777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G777" s="5"/>
+      <c r="AA777" s="4"/>
+    </row>
+    <row r="778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G778" s="5"/>
+      <c r="AA778" s="4"/>
+    </row>
+    <row r="779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G779" s="5"/>
+      <c r="AA779" s="4"/>
+    </row>
+    <row r="780" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G780" s="5"/>
+      <c r="AA780" s="4"/>
+    </row>
+    <row r="781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G781" s="5"/>
+      <c r="AA781" s="4"/>
+    </row>
+    <row r="782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G782" s="5"/>
+      <c r="AA782" s="4"/>
+    </row>
+    <row r="783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G783" s="5"/>
+      <c r="AA783" s="4"/>
+    </row>
+    <row r="784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G784" s="5"/>
+      <c r="AA784" s="4"/>
+    </row>
+    <row r="785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G785" s="5"/>
+      <c r="AA785" s="4"/>
+    </row>
+    <row r="786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G786" s="5"/>
+      <c r="AA786" s="4"/>
+    </row>
+    <row r="787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G787" s="5"/>
+      <c r="AA787" s="4"/>
+    </row>
+    <row r="788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G788" s="5"/>
+      <c r="AA788" s="4"/>
+    </row>
+    <row r="789" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G789" s="5"/>
+      <c r="AA789" s="4"/>
+    </row>
+    <row r="790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G790" s="5"/>
+      <c r="AA790" s="4"/>
+    </row>
+    <row r="791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G791" s="5"/>
+      <c r="AA791" s="4"/>
+    </row>
+    <row r="792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G792" s="5"/>
+      <c r="AA792" s="4"/>
+    </row>
+    <row r="793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G793" s="5"/>
+      <c r="AA793" s="4"/>
+    </row>
+    <row r="794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G794" s="5"/>
+      <c r="AA794" s="4"/>
+    </row>
+    <row r="795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G795" s="5"/>
+      <c r="AA795" s="4"/>
+    </row>
+    <row r="796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G796" s="5"/>
+      <c r="AA796" s="4"/>
+    </row>
+    <row r="797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G797" s="5"/>
+      <c r="AA797" s="4"/>
+    </row>
+    <row r="798" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G798" s="5"/>
+      <c r="AA798" s="4"/>
+    </row>
+    <row r="799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G799" s="5"/>
+      <c r="AA799" s="4"/>
+    </row>
+    <row r="800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G800" s="5"/>
+      <c r="AA800" s="4"/>
+    </row>
+    <row r="801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G801" s="5"/>
+      <c r="AA801" s="4"/>
+    </row>
+    <row r="802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G802" s="5"/>
+      <c r="AA802" s="4"/>
+    </row>
+    <row r="803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G803" s="5"/>
+      <c r="AA803" s="4"/>
+    </row>
+    <row r="804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G804" s="5"/>
+      <c r="AA804" s="4"/>
+    </row>
+    <row r="805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G805" s="5"/>
+      <c r="AA805" s="4"/>
+    </row>
+    <row r="806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G806" s="5"/>
+      <c r="AA806" s="4"/>
+    </row>
+    <row r="807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G807" s="5"/>
+      <c r="AA807" s="4"/>
+    </row>
+    <row r="808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G808" s="5"/>
+      <c r="AA808" s="4"/>
+    </row>
+    <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G809" s="5"/>
+      <c r="AA809" s="4"/>
+    </row>
+    <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G810" s="5"/>
+      <c r="AA810" s="4"/>
+    </row>
+    <row r="811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G811" s="5"/>
+      <c r="AA811" s="4"/>
+    </row>
+    <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G812" s="5"/>
+      <c r="AA812" s="4"/>
+    </row>
+    <row r="813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G813" s="5"/>
+      <c r="AA813" s="4"/>
+    </row>
+    <row r="814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G814" s="5"/>
+      <c r="AA814" s="4"/>
+    </row>
+    <row r="815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G815" s="5"/>
+      <c r="AA815" s="4"/>
+    </row>
+    <row r="816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G816" s="5"/>
+      <c r="AA816" s="4"/>
+    </row>
+    <row r="817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G817" s="5"/>
+      <c r="AA817" s="4"/>
+    </row>
+    <row r="818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G818" s="5"/>
+      <c r="AA818" s="4"/>
+    </row>
+    <row r="819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G819" s="5"/>
+      <c r="AA819" s="4"/>
+    </row>
+    <row r="820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G820" s="5"/>
+      <c r="AA820" s="4"/>
+    </row>
+    <row r="821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G821" s="5"/>
+      <c r="AA821" s="4"/>
+    </row>
+    <row r="822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G822" s="5"/>
+      <c r="AA822" s="4"/>
+    </row>
+    <row r="823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G823" s="5"/>
+      <c r="AA823" s="4"/>
+    </row>
+    <row r="824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G824" s="5"/>
+      <c r="AA824" s="4"/>
+    </row>
+    <row r="825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G825" s="5"/>
+      <c r="AA825" s="4"/>
+    </row>
+    <row r="826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G826" s="5"/>
+      <c r="AA826" s="4"/>
+    </row>
+    <row r="827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G827" s="5"/>
+      <c r="AA827" s="4"/>
+    </row>
+    <row r="828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G828" s="5"/>
+      <c r="AA828" s="4"/>
+    </row>
+    <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G829" s="5"/>
+      <c r="AA829" s="4"/>
+    </row>
+    <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G830" s="5"/>
+      <c r="AA830" s="4"/>
+    </row>
+    <row r="831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G831" s="5"/>
+      <c r="AA831" s="4"/>
+    </row>
+    <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G832" s="5"/>
+      <c r="AA832" s="4"/>
+    </row>
+    <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G833" s="5"/>
+      <c r="AA833" s="4"/>
+    </row>
+    <row r="834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G834" s="5"/>
+      <c r="AA834" s="4"/>
+    </row>
+    <row r="835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G835" s="5"/>
+      <c r="AA835" s="4"/>
+    </row>
+    <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G836" s="5"/>
+      <c r="AA836" s="4"/>
+    </row>
+    <row r="837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G837" s="5"/>
+      <c r="AA837" s="4"/>
+    </row>
+    <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G838" s="5"/>
+      <c r="AA838" s="4"/>
+    </row>
+    <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G839" s="5"/>
+      <c r="AA839" s="4"/>
+    </row>
+    <row r="840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G840" s="5"/>
+      <c r="AA840" s="4"/>
+    </row>
+    <row r="841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G841" s="5"/>
+      <c r="AA841" s="4"/>
+    </row>
+    <row r="842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G842" s="5"/>
+      <c r="AA842" s="4"/>
+    </row>
+    <row r="843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G843" s="5"/>
+      <c r="AA843" s="4"/>
+    </row>
+    <row r="844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G844" s="5"/>
+      <c r="AA844" s="4"/>
+    </row>
+    <row r="845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G845" s="5"/>
+      <c r="AA845" s="4"/>
+    </row>
+    <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G846" s="5"/>
+      <c r="AA846" s="4"/>
+    </row>
+    <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G847" s="5"/>
+      <c r="AA847" s="4"/>
+    </row>
+    <row r="848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G848" s="5"/>
+      <c r="AA848" s="4"/>
+    </row>
+    <row r="849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G849" s="5"/>
+      <c r="AA849" s="4"/>
+    </row>
+    <row r="850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G850" s="5"/>
+      <c r="AA850" s="4"/>
+    </row>
+    <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G851" s="5"/>
+      <c r="AA851" s="4"/>
+    </row>
+    <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G852" s="5"/>
+      <c r="AA852" s="4"/>
+    </row>
+    <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G853" s="5"/>
+      <c r="AA853" s="4"/>
+    </row>
+    <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G854" s="5"/>
+      <c r="AA854" s="4"/>
+    </row>
+    <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G855" s="5"/>
+      <c r="AA855" s="4"/>
+    </row>
+    <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G856" s="5"/>
+      <c r="AA856" s="4"/>
+    </row>
+    <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G857" s="5"/>
+      <c r="AA857" s="4"/>
+    </row>
+    <row r="858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G858" s="5"/>
+      <c r="AA858" s="4"/>
+    </row>
+    <row r="859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G859" s="5"/>
+      <c r="AA859" s="4"/>
+    </row>
+    <row r="860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G860" s="5"/>
+      <c r="AA860" s="4"/>
+    </row>
+    <row r="861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G861" s="5"/>
+      <c r="AA861" s="4"/>
+    </row>
+    <row r="862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G862" s="5"/>
+      <c r="AA862" s="4"/>
+    </row>
+    <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G863" s="5"/>
+      <c r="AA863" s="4"/>
+    </row>
+    <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G864" s="5"/>
+      <c r="AA864" s="4"/>
+    </row>
+    <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G865" s="5"/>
+      <c r="AA865" s="4"/>
+    </row>
+    <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G866" s="5"/>
+      <c r="AA866" s="4"/>
+    </row>
+    <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G867" s="5"/>
+      <c r="AA867" s="4"/>
+    </row>
+    <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G868" s="5"/>
+      <c r="AA868" s="4"/>
+    </row>
+    <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G869" s="5"/>
+      <c r="AA869" s="4"/>
+    </row>
+    <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G870" s="5"/>
+      <c r="AA870" s="4"/>
+    </row>
+    <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G871" s="5"/>
+      <c r="AA871" s="4"/>
+    </row>
+    <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G872" s="5"/>
+      <c r="AA872" s="4"/>
+    </row>
+    <row r="873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G873" s="5"/>
+      <c r="AA873" s="4"/>
+    </row>
+    <row r="874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G874" s="5"/>
+      <c r="AA874" s="4"/>
+    </row>
+    <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G875" s="5"/>
+      <c r="AA875" s="4"/>
+    </row>
+    <row r="876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G876" s="5"/>
+      <c r="AA876" s="4"/>
+    </row>
+    <row r="877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G877" s="5"/>
+      <c r="AA877" s="4"/>
+    </row>
+    <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G878" s="5"/>
+      <c r="AA878" s="4"/>
+    </row>
+    <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G879" s="5"/>
+      <c r="AA879" s="4"/>
+    </row>
+    <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G880" s="5"/>
+      <c r="AA880" s="4"/>
+    </row>
+    <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G881" s="5"/>
+      <c r="AA881" s="4"/>
+    </row>
+    <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G882" s="5"/>
+      <c r="AA882" s="4"/>
+    </row>
+    <row r="883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G883" s="5"/>
+      <c r="AA883" s="4"/>
+    </row>
+    <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G884" s="5"/>
+      <c r="AA884" s="4"/>
+    </row>
+    <row r="885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G885" s="5"/>
+      <c r="AA885" s="4"/>
+    </row>
+    <row r="886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G886" s="5"/>
+      <c r="AA886" s="4"/>
+    </row>
+    <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G887" s="5"/>
+      <c r="AA887" s="4"/>
+    </row>
+    <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G888" s="5"/>
+      <c r="AA888" s="4"/>
+    </row>
+    <row r="889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G889" s="5"/>
+      <c r="AA889" s="4"/>
+    </row>
+    <row r="890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G890" s="5"/>
+      <c r="AA890" s="4"/>
+    </row>
+    <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G891" s="5"/>
+      <c r="AA891" s="4"/>
+    </row>
+    <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G892" s="5"/>
+      <c r="AA892" s="4"/>
+    </row>
+    <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G893" s="5"/>
+      <c r="AA893" s="4"/>
+    </row>
+    <row r="894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G894" s="5"/>
+      <c r="AA894" s="4"/>
+    </row>
+    <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G895" s="5"/>
+      <c r="AA895" s="4"/>
+    </row>
+    <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G896" s="5"/>
+      <c r="AA896" s="4"/>
+    </row>
+    <row r="897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G897" s="5"/>
+      <c r="AA897" s="4"/>
+    </row>
+    <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G898" s="5"/>
+      <c r="AA898" s="4"/>
+    </row>
+    <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G899" s="5"/>
+      <c r="AA899" s="4"/>
+    </row>
+    <row r="900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G900" s="5"/>
+      <c r="AA900" s="4"/>
+    </row>
+    <row r="901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G901" s="5"/>
+      <c r="AA901" s="4"/>
+    </row>
+    <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G902" s="5"/>
+      <c r="AA902" s="4"/>
+    </row>
+    <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G903" s="5"/>
+      <c r="AA903" s="4"/>
+    </row>
+    <row r="904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G904" s="5"/>
+      <c r="AA904" s="4"/>
+    </row>
+    <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G905" s="5"/>
+      <c r="AA905" s="4"/>
+    </row>
+    <row r="906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G906" s="5"/>
+      <c r="AA906" s="4"/>
+    </row>
+    <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G907" s="5"/>
+      <c r="AA907" s="4"/>
+    </row>
+    <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G908" s="5"/>
+      <c r="AA908" s="4"/>
+    </row>
+    <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G909" s="5"/>
+      <c r="AA909" s="4"/>
+    </row>
+    <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G910" s="5"/>
+      <c r="AA910" s="4"/>
+    </row>
+    <row r="911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G911" s="5"/>
+      <c r="AA911" s="4"/>
+    </row>
+    <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G912" s="5"/>
+      <c r="AA912" s="4"/>
+    </row>
+    <row r="913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G913" s="5"/>
+      <c r="AA913" s="4"/>
+    </row>
+    <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G914" s="5"/>
+      <c r="AA914" s="4"/>
+    </row>
+    <row r="915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G915" s="5"/>
+      <c r="AA915" s="4"/>
+    </row>
+    <row r="916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G916" s="5"/>
+      <c r="AA916" s="4"/>
+    </row>
+    <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G917" s="5"/>
+      <c r="AA917" s="4"/>
+    </row>
+    <row r="918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G918" s="5"/>
+      <c r="AA918" s="4"/>
+    </row>
+    <row r="919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G919" s="5"/>
+      <c r="AA919" s="4"/>
+    </row>
+    <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G920" s="5"/>
+      <c r="AA920" s="4"/>
+    </row>
+    <row r="921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G921" s="5"/>
+      <c r="AA921" s="4"/>
+    </row>
+    <row r="922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G922" s="5"/>
+      <c r="AA922" s="4"/>
+    </row>
+    <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G923" s="5"/>
+      <c r="AA923" s="4"/>
+    </row>
+    <row r="924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G924" s="5"/>
+      <c r="AA924" s="4"/>
+    </row>
+    <row r="925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G925" s="5"/>
+      <c r="AA925" s="4"/>
+    </row>
+    <row r="926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G926" s="5"/>
+      <c r="AA926" s="4"/>
+    </row>
+    <row r="927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G927" s="5"/>
+      <c r="AA927" s="4"/>
+    </row>
+    <row r="928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G928" s="5"/>
+      <c r="AA928" s="4"/>
+    </row>
+    <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G929" s="5"/>
+      <c r="AA929" s="4"/>
+    </row>
+    <row r="930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G930" s="5"/>
+      <c r="AA930" s="4"/>
+    </row>
+    <row r="931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G931" s="5"/>
+      <c r="AA931" s="4"/>
+    </row>
+    <row r="932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G932" s="5"/>
+      <c r="AA932" s="4"/>
+    </row>
+    <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G933" s="5"/>
+      <c r="AA933" s="4"/>
+    </row>
+    <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G934" s="5"/>
+      <c r="AA934" s="4"/>
+    </row>
+    <row r="935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G935" s="5"/>
+      <c r="AA935" s="4"/>
+    </row>
+    <row r="936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G936" s="5"/>
+      <c r="AA936" s="4"/>
+    </row>
+    <row r="937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G937" s="5"/>
+      <c r="AA937" s="4"/>
+    </row>
+    <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G938" s="5"/>
+      <c r="AA938" s="4"/>
+    </row>
+    <row r="939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G939" s="5"/>
+      <c r="AA939" s="4"/>
+    </row>
+    <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G940" s="5"/>
+      <c r="AA940" s="4"/>
+    </row>
+    <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G941" s="5"/>
+      <c r="AA941" s="4"/>
+    </row>
+    <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G942" s="5"/>
+      <c r="AA942" s="4"/>
+    </row>
+    <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G943" s="5"/>
+      <c r="AA943" s="4"/>
+    </row>
+    <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G944" s="5"/>
+      <c r="AA944" s="4"/>
+    </row>
+    <row r="945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G945" s="5"/>
+      <c r="AA945" s="4"/>
+    </row>
+    <row r="946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G946" s="5"/>
+      <c r="AA946" s="4"/>
+    </row>
+    <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G947" s="5"/>
+      <c r="AA947" s="4"/>
+    </row>
+    <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G948" s="5"/>
+      <c r="AA948" s="4"/>
+    </row>
+    <row r="949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G949" s="5"/>
+      <c r="AA949" s="4"/>
+    </row>
+    <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G950" s="5"/>
+      <c r="AA950" s="4"/>
+    </row>
+    <row r="951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G951" s="5"/>
+      <c r="AA951" s="4"/>
+    </row>
+    <row r="952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G952" s="5"/>
+      <c r="AA952" s="4"/>
+    </row>
+    <row r="953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G953" s="5"/>
+      <c r="AA953" s="4"/>
+    </row>
+    <row r="954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G954" s="5"/>
+      <c r="AA954" s="4"/>
+    </row>
+    <row r="955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G955" s="5"/>
+      <c r="AA955" s="4"/>
+    </row>
+    <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G956" s="5"/>
+      <c r="AA956" s="4"/>
+    </row>
+    <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G957" s="5"/>
+      <c r="AA957" s="4"/>
+    </row>
+    <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G958" s="5"/>
+      <c r="AA958" s="4"/>
+    </row>
+    <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G959" s="5"/>
+      <c r="AA959" s="4"/>
+    </row>
+    <row r="960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G960" s="5"/>
+      <c r="AA960" s="4"/>
+    </row>
+    <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G961" s="5"/>
+      <c r="AA961" s="4"/>
+    </row>
+    <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G962" s="5"/>
+      <c r="AA962" s="4"/>
+    </row>
+    <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G963" s="5"/>
+      <c r="AA963" s="4"/>
+    </row>
+    <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G964" s="5"/>
+      <c r="AA964" s="4"/>
+    </row>
+    <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G965" s="5"/>
+      <c r="AA965" s="4"/>
+    </row>
+    <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G966" s="5"/>
+      <c r="AA966" s="4"/>
+    </row>
+    <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G967" s="5"/>
+      <c r="AA967" s="4"/>
+    </row>
+    <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G968" s="5"/>
+      <c r="AA968" s="4"/>
+    </row>
+    <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G969" s="5"/>
+      <c r="AA969" s="4"/>
+    </row>
+    <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G970" s="5"/>
+      <c r="AA970" s="4"/>
+    </row>
+    <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G971" s="5"/>
+      <c r="AA971" s="4"/>
+    </row>
+    <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G972" s="5"/>
+      <c r="AA972" s="4"/>
+    </row>
+    <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G973" s="5"/>
+      <c r="AA973" s="4"/>
+    </row>
+    <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G974" s="5"/>
+      <c r="AA974" s="4"/>
+    </row>
+    <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G975" s="5"/>
+      <c r="AA975" s="4"/>
+    </row>
+    <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G976" s="5"/>
+      <c r="AA976" s="4"/>
+    </row>
+    <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G977" s="5"/>
+      <c r="AA977" s="4"/>
+    </row>
+    <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G978" s="5"/>
+      <c r="AA978" s="4"/>
+    </row>
+    <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G979" s="5"/>
+      <c r="AA979" s="4"/>
+    </row>
+    <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G980" s="5"/>
+      <c r="AA980" s="4"/>
+    </row>
+    <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G981" s="5"/>
+      <c r="AA981" s="4"/>
+    </row>
+    <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G982" s="5"/>
+      <c r="AA982" s="4"/>
+    </row>
+    <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G983" s="5"/>
+      <c r="AA983" s="4"/>
+    </row>
+    <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G984" s="5"/>
+      <c r="AA984" s="4"/>
+    </row>
+    <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G985" s="5"/>
+      <c r="AA985" s="4"/>
+    </row>
+    <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G986" s="5"/>
+      <c r="AA986" s="4"/>
+    </row>
+    <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G987" s="5"/>
+      <c r="AA987" s="4"/>
+    </row>
+    <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G988" s="5"/>
+      <c r="AA988" s="4"/>
+    </row>
+    <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G989" s="5"/>
+      <c r="AA989" s="4"/>
+    </row>
+    <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G990" s="5"/>
+      <c r="AA990" s="4"/>
+    </row>
+    <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G991" s="5"/>
+      <c r="AA991" s="4"/>
+    </row>
+    <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G992" s="5"/>
+      <c r="AA992" s="4"/>
+    </row>
+    <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G993" s="5"/>
+      <c r="AA993" s="4"/>
+    </row>
+    <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G994" s="5"/>
+      <c r="AA994" s="4"/>
+    </row>
+    <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G995" s="5"/>
+      <c r="AA995" s="4"/>
+    </row>
+    <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G996" s="5"/>
+      <c r="AA996" s="4"/>
+    </row>
+    <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G997" s="5"/>
+      <c r="AA997" s="4"/>
+    </row>
+    <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G998" s="5"/>
+      <c r="AA998" s="4"/>
+    </row>
+    <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G999" s="5"/>
+      <c r="AA999" s="4"/>
+    </row>
+    <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1000" s="5"/>
+      <c r="AA1000" s="4"/>
+    </row>
+    <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1001" s="5"/>
+      <c r="AA1001" s="4"/>
+    </row>
+    <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1002" s="5"/>
+      <c r="AA1002" s="4"/>
+    </row>
+    <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1003" s="5"/>
+      <c r="AA1003" s="4"/>
+    </row>
+    <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1004" s="5"/>
+      <c r="AA1004" s="4"/>
+    </row>
+    <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1005" s="5"/>
+      <c r="AA1005" s="4"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AA2:AA1005" type="list">
+      <formula1>Feuille1!$AW$4:$AW$5</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G1005" type="list">
+      <formula1>Feuille1!$AX$4:$AX$5</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
